--- a/analises/2026-09-28-del-maipo-vinhos-especiais.xlsx
+++ b/analises/2026-09-28-del-maipo-vinhos-especiais.xlsx
@@ -455,7 +455,7 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="80" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -511,7 +511,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Venda (R$)</t>
+          <t>Preço de venda comnéctar (R$)</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -8008,7 +8008,6 @@
           <t>Marc de Champagne Moët &amp; Chandon</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
           <t>750 ml</t>

--- a/analises/2026-09-28-del-maipo-vinhos-especiais.xlsx
+++ b/analises/2026-09-28-del-maipo-vinhos-especiais.xlsx
@@ -455,7 +455,7 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="80" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -511,7 +511,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Preço de venda comnéctar (R$)</t>
+          <t>Venda (R$)</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -8008,6 +8008,7 @@
           <t>Marc de Champagne Moët &amp; Chandon</t>
         </is>
       </c>
+      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
           <t>750 ml</t>
